--- a/action_cop/output_excels/15_Further_Issues_XBRL_Filings.xlsx
+++ b/action_cop/output_excels/15_Further_Issues_XBRL_Filings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q114"/>
+  <dimension ref="A1:Q116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1524,44 +1524,42 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>72364</t>
-        </is>
+      <c r="A15" t="n">
+        <v>53094</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24-SEP-2026</t>
+          <t>10-OCT-2024</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wheels India Limited</t>
+          <t>SANSERA ENGINEERING LIMITED</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>L35921TN1960PLC004175</t>
+          <t>L34103KA1981PLC004542</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>10-JUL-2026</t>
+          <t>20-AUG-2024</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>12-AUG-2026</t>
+          <t>26-SEP-2024</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>24-SEP-2026</t>
+          <t>10-OCT-2024</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>INE715A01015</t>
+          <t>INE953O01021</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1571,37 +1569,29 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>NSE,NSE</t>
+          <t>NSE,BSE</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>WHEELS</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
+          <t>SANSERA</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.05</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>In-Principle</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>5.27 KB</t>
-        </is>
-      </c>
+      <c r="N15" t="n">
+        <v>12000000000</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1727355_24092026015924_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1265223_10102024061811_WEB.xml</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1611,44 +1601,42 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>72059</t>
-        </is>
+      <c r="A16" t="n">
+        <v>53034</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>22-SEP-2026</t>
+          <t>09-OCT-2024</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Inox Green Energy Services Limited</t>
+          <t>Adani Enterprises Limited</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>L45207GJ2012PLC070279</t>
+          <t>L51100GJ1993PLC019067</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>22-JUL-2026</t>
+          <t>28-MAY-2024</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>13-AUG-2026</t>
+          <t>24-JUN-2024</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>16-SEP-2026</t>
+          <t>09-OCT-2024</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>INE510W01014</t>
+          <t>INE423A01024</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1663,32 +1651,24 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>INOXGREEN</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0.05</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
           <t>In-Principle</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>4000000000</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>7.40 KB</t>
-        </is>
-      </c>
+      <c r="N16" t="n">
+        <v>166000000000</v>
+      </c>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1724645_16092026044948_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1262960_09102024022518_WEB.xml</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1700,42 +1680,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>72268</t>
+          <t>72679</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>22-SEP-2026</t>
+          <t>07-OCT-2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ADITYA INFOTECH LIMITED</t>
+          <t>TD POWER SYSTEMS LIMITED</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>L74899DL1995PLC066784</t>
+          <t>L31103KA1999PLC025071</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>19-AUG-2026</t>
+          <t>14-AUG-2026</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>19-SEP-2026</t>
+          <t>10-SEP-2026</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22-SEP-2026</t>
+          <t>07-OCT-2026</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>INE819V01029</t>
+          <t>INE419M01035</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1745,12 +1725,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>NSE,BSE</t>
+          <t>BSE,NSE</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>CPPLUS</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1765,64 +1745,64 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>15000000000</t>
+          <t>6000000000</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>8.00 KB</t>
+          <t>6.50 KB</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1726274_22092026021359_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1733671_07102026121115_WEB.xml</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>72095</t>
+          <t>72658</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17-SEP-2026</t>
+          <t>06-OCT-2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bharat Forge Limited</t>
+          <t>PTC INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>L25209PN1961PLC012046</t>
+          <t>L27109UP1963PLC002931</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>10-AUG-2026</t>
+          <t>27-JUN-2026</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>11-SEP-2026</t>
+          <t>01-AUG-2026</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>17-SEP-2026</t>
+          <t>06-OCT-2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>INE465A01025</t>
+          <t>INE596F01018</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1837,7 +1817,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>PTCIL</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1852,64 +1832,64 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>20000000000</t>
+          <t>18000000000</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>8.55 KB</t>
+          <t>9.42 KB</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1724955_17092026032518_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1733417_06102026035659_WEB.xml</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>71898</t>
+          <t>72364</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10-SEP-2026</t>
+          <t>24-SEP-2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Neogen Chemicals Limited</t>
+          <t>Wheels India Limited</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>L24200MH1989PLC050919</t>
+          <t>L35921TN1960PLC004175</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>24-JUL-2026</t>
+          <t>10-JUL-2026</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>21-AUG-2026</t>
+          <t>12-AUG-2026</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>10-SEP-2026</t>
+          <t>24-SEP-2026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>INE136S01016</t>
+          <t>INE715A01015</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1919,12 +1899,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>BSE,NSE</t>
+          <t>NSE,NSE</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>WHEELS</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1939,64 +1919,64 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>6000000000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>6.25 KB</t>
+          <t>5.27 KB</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1723185_10092026120405_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1727355_24092026015924_WEB.xml</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>71391</t>
+          <t>72059</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>25-AUG-2026</t>
+          <t>22-SEP-2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Gujarat Themis Biosyn Limited</t>
+          <t>Inox Green Energy Services Limited</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>L24230GJ1981PLC004878</t>
+          <t>L45207GJ2012PLC070279</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>06-JUN-2026</t>
+          <t>22-JUL-2026</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>22-AUG-2026</t>
+          <t>13-AUG-2026</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>25-AUG-2026</t>
+          <t>16-SEP-2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>INE942C01045</t>
+          <t>INE510W01014</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2011,7 +1991,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>GUJTHEM</t>
+          <t>INOXGREEN</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2026,64 +2006,64 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>7500000000</t>
+          <t>4000000000</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>9.49 KB</t>
+          <t>7.40 KB</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1717854_25082026073426_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1724645_16092026044948_WEB.xml</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>71335</t>
+          <t>72268</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>24-AUG-2026</t>
+          <t>22-SEP-2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Piramal Finance Limited</t>
+          <t>ADITYA INFOTECH LIMITED</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>L64910MH1984PLC032639</t>
+          <t>L74899DL1995PLC066784</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>16-JUL-2026</t>
+          <t>19-AUG-2026</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>17-AUG-2026</t>
+          <t>19-SEP-2026</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>24-AUG-2026</t>
+          <t>22-SEP-2026</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>INE202B01038</t>
+          <t>INE819V01029</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2098,7 +2078,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>PIRAMALFIN</t>
+          <t>CPPLUS</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2113,64 +2093,64 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>21000000000</t>
+          <t>15000000000</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>8.25 KB</t>
+          <t>8.00 KB</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1717277_24082026032807_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1726274_22092026021359_WEB.xml</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>71101</t>
+          <t>72095</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17-AUG-2026</t>
+          <t>17-SEP-2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SPR Auto Technologies Limited</t>
+          <t>Bharat Forge Limited</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>L29112DL1963PLC004084</t>
+          <t>L25209PN1961PLC012046</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>11-MAY-2026</t>
+          <t>10-AUG-2026</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>27-JUL-2026</t>
+          <t>11-SEP-2026</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>17-AUG-2026</t>
+          <t>17-SEP-2026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>INE526E01018</t>
+          <t>INE465A01025</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2180,12 +2160,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>NSE,BSE</t>
+          <t>BSE,NSE</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2200,64 +2180,64 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>10000000000</t>
+          <t>20000000000</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>6.20 KB</t>
+          <t>8.55 KB</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1715360_17082026042749_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1724955_17092026032518_WEB.xml</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>71106</t>
+          <t>71898</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>17-AUG-2026</t>
+          <t>10-SEP-2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netweb Technologies India Limited</t>
+          <t>Neogen Chemicals Limited</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>L72100HR1999PLC103911</t>
+          <t>L24200MH1989PLC050919</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>01-JUL-2026</t>
+          <t>24-JUL-2026</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>01-AUG-2026</t>
+          <t>21-AUG-2026</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>17-AUG-2026</t>
+          <t>10-SEP-2026</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>INE0NT901020</t>
+          <t>INE136S01016</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2267,12 +2247,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>NSE,BSE</t>
+          <t>BSE,NSE</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2287,64 +2267,64 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>12000000000</t>
+          <t>6000000000</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>6.90 KB</t>
+          <t>6.25 KB</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1715333_17082026031125_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1723185_10092026120405_WEB.xml</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>70861</t>
+          <t>71391</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10-AUG-2026</t>
+          <t>25-AUG-2026</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>APAR Industries Limited</t>
+          <t>Gujarat Themis Biosyn Limited</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>L91110GJ1989PLC012802</t>
+          <t>L24230GJ1981PLC004878</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>30-JUN-2026</t>
+          <t>06-JUN-2026</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>30-JUL-2026</t>
+          <t>22-AUG-2026</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>10-AUG-2026</t>
+          <t>25-AUG-2026</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>INE372A01015</t>
+          <t>INE942C01045</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2359,7 +2339,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>APARINDS</t>
+          <t>GUJTHEM</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2374,64 +2354,64 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>25000000000</t>
+          <t>7500000000</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>6.64 KB</t>
+          <t>9.49 KB</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1710805_10082026112852_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1717854_25082026073426_WEB.xml</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>70701</t>
+          <t>71335</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>04-AUG-2026</t>
+          <t>24-AUG-2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Globus Spirits Limited</t>
+          <t>Piramal Finance Limited</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>L74899DL1993PLC052177</t>
+          <t>L64910MH1984PLC032639</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20-NOV-2025</t>
+          <t>16-JUL-2026</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>18-DEC-2025</t>
+          <t>17-AUG-2026</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>04-AUG-2026</t>
+          <t>24-AUG-2026</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>INE615I01010</t>
+          <t>INE202B01038</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2446,7 +2426,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>GLOBUSSPR</t>
+          <t>PIRAMALFIN</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2461,64 +2441,64 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2000000000</t>
+          <t>21000000000</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>4.92 KB</t>
+          <t>8.25 KB</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1707427_04082026023534_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1717277_24082026032807_WEB.xml</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>70667</t>
+          <t>71101</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>03-AUG-2026</t>
+          <t>17-AUG-2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Arvind Limited</t>
+          <t>SPR Auto Technologies Limited</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>L17119GJ1931PLC000093</t>
+          <t>L29112DL1963PLC004084</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>03-JUL-2026</t>
+          <t>11-MAY-2026</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>02-AUG-2026</t>
+          <t>27-JUL-2026</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>03-AUG-2026</t>
+          <t>17-AUG-2026</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>INE034A01011</t>
+          <t>INE526E01018</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2528,12 +2508,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>BSE,NSE</t>
+          <t>NSE,BSE</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2548,64 +2528,64 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>6000000000</t>
+          <t>10000000000</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>5.88 KB</t>
+          <t>6.20 KB</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1706799_03082026123828_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1715360_17082026042749_WEB.xml</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>70586</t>
+          <t>71106</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>30-JUL-2026</t>
+          <t>17-AUG-2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>P N GADGIL JEWELLERS LIMITED</t>
+          <t>Netweb Technologies India Limited</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>L36912PN2013PLC149288</t>
+          <t>L72100HR1999PLC103911</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>03-JUL-2025</t>
+          <t>01-JUL-2026</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>18-AUG-2025</t>
+          <t>01-AUG-2026</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>30-JUL-2026</t>
+          <t>17-AUG-2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>INE953R01016</t>
+          <t>INE0NT901020</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2620,7 +2600,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>PNGJL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2635,64 +2615,64 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>7000000000</t>
+          <t>12000000000</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>6.35 KB</t>
+          <t>6.90 KB</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1705012_30072026025653_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1715333_17082026031125_WEB.xml</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>70465</t>
+          <t>70861</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>27-JUL-2026</t>
+          <t>10-AUG-2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ADANI ENERGY SOLUTIONS LIMITED</t>
+          <t>APAR Industries Limited</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>L40300GJ2013PLC077803</t>
+          <t>L91110GJ1989PLC012802</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>01-JUL-2026</t>
+          <t>30-JUN-2026</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>25-JUL-2026</t>
+          <t>30-JUL-2026</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>27-JUL-2026</t>
+          <t>10-AUG-2026</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>INE931S01010</t>
+          <t>INE372A01015</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2707,7 +2687,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>APARINDS</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2722,64 +2702,64 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>100000000000</t>
+          <t>25000000000</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>9.35 KB</t>
+          <t>6.64 KB</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1701698_27072026100125_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1710805_10082026112852_WEB.xml</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>70464</t>
+          <t>70701</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>27-JUL-2026</t>
+          <t>04-AUG-2026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hilton Metal Forging Limited</t>
+          <t>Globus Spirits Limited</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>L28900MH2005PLC154986</t>
+          <t>L74899DL1993PLC052177</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>18-JUN-2026</t>
+          <t>20-NOV-2025</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>15-JUL-2026</t>
+          <t>18-DEC-2025</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>26-JUL-2026</t>
+          <t>04-AUG-2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>INE788H01017</t>
+          <t>INE615I01010</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2789,12 +2769,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>BSE,NSE</t>
+          <t>NSE,BSE</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>HILTON</t>
+          <t>GLOBUSSPR</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2809,64 +2789,64 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>430000000</t>
+          <t>2000000000</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>6.32 KB</t>
+          <t>4.92 KB</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1701676_26072026050348_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1707427_04082026023534_WEB.xml</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>70418</t>
+          <t>70667</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>23-JUL-2026</t>
+          <t>03-AUG-2026</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Diamond Power Infrastructure Limited</t>
+          <t>Arvind Limited</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>L31300GJ1992PLC018198</t>
+          <t>L17119GJ1931PLC000093</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>18-JUN-2026</t>
+          <t>03-JUL-2026</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>19-JUL-2026</t>
+          <t>02-AUG-2026</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>23-JUL-2026</t>
+          <t>03-AUG-2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>INE989C01038</t>
+          <t>INE034A01011</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2881,7 +2861,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2896,64 +2876,64 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>16150000000</t>
+          <t>6000000000</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>8.69 KB</t>
+          <t>5.88 KB</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1700383_23072026082312_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1706799_03082026123828_WEB.xml</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>70231</t>
+          <t>70586</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>15-JUL-2026</t>
+          <t>30-JUL-2026</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ATHER ENERGY LIMITED</t>
+          <t>P N GADGIL JEWELLERS LIMITED</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>L40100KA2013PLC093769</t>
+          <t>L36912PN2013PLC149288</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12-JUN-2026</t>
+          <t>03-JUL-2025</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>14-JUL-2026</t>
+          <t>18-AUG-2025</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>15-JUL-2026</t>
+          <t>30-JUL-2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>INE0LEZ01016</t>
+          <t>INE953R01016</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2968,7 +2948,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>PNGJL</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2983,64 +2963,64 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>13000000000</t>
+          <t>7000000000</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>14.29 KB</t>
+          <t>6.35 KB</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1693377_15072026052102_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1705012_30072026025653_WEB.xml</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>70191</t>
+          <t>70465</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14-JUL-2026</t>
+          <t>27-JUL-2026</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BELRISE INDUSTRIES LIMITED</t>
+          <t>ADANI ENERGY SOLUTIONS LIMITED</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>L73100MH1996PLC102827</t>
+          <t>L40300GJ2013PLC077803</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>24-MAY-2026</t>
+          <t>01-JUL-2026</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>30-JUN-2026</t>
+          <t>25-JUL-2026</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>14-JUL-2026</t>
+          <t>27-JUL-2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>INE894V01022</t>
+          <t>INE931S01010</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3055,7 +3035,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>BELRISE</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3070,64 +3050,64 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>19000000000</t>
+          <t>100000000000</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>7.25 KB</t>
+          <t>9.35 KB</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1692344_14072026045244_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1701698_27072026100125_WEB.xml</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>69970</t>
+          <t>70464</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>06-JUL-2026</t>
+          <t>27-JUL-2026</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Blue Jet Healthcare Limited</t>
+          <t>Hilton Metal Forging Limited</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>L99999MH1968PLC014154</t>
+          <t>L28900MH2005PLC154986</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>25-MAY-2026</t>
+          <t>18-JUN-2026</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>17-JUN-2026</t>
+          <t>15-JUL-2026</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>06-JUL-2026</t>
+          <t>26-JUL-2026</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>INE0KBH01020</t>
+          <t>INE788H01017</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3142,7 +3122,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>BLUEJET</t>
+          <t>HILTON</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3157,64 +3137,64 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>10000000000</t>
+          <t>430000000</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>7.92 KB</t>
+          <t>6.32 KB</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1688379_06072026021522_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1701676_26072026050348_WEB.xml</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>69767</t>
+          <t>70418</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>29-JUN-2026</t>
+          <t>23-JUL-2026</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Manorama Industries Limited</t>
+          <t>Diamond Power Infrastructure Limited</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>L15142MH2005PLC243687</t>
+          <t>L31300GJ1992PLC018198</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>12-MAR-2026</t>
+          <t>18-JUN-2026</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>19-APR-2026</t>
+          <t>19-JUL-2026</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>29-JUN-2026</t>
+          <t>23-JUL-2026</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>INE00VM01036</t>
+          <t>INE989C01038</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3229,7 +3209,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3244,64 +3224,64 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>5000000000</t>
+          <t>16150000000</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>6.09 KB</t>
+          <t>8.69 KB</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1685961_29062026032813_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1700383_23072026082312_WEB.xml</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>69538</t>
+          <t>70231</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>22-JUN-2026</t>
+          <t>15-JUL-2026</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>JSW INFRASTRUCTURE LIMITED</t>
+          <t>ATHER ENERGY LIMITED</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>L45200MH2006PLC161268</t>
+          <t>L40100KA2013PLC093769</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>20-FEB-2026</t>
+          <t>12-JUN-2026</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>23-MAR-2026</t>
+          <t>14-JUL-2026</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>22-JUN-2026</t>
+          <t>15-JUL-2026</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>INE880J01026</t>
+          <t>INE0LEZ01016</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3311,12 +3291,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>BSE,NSE</t>
+          <t>NSE,BSE</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>JSWINFRA</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3331,64 +3311,64 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13000000000</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>10.49 KB</t>
+          <t>14.29 KB</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1683149_22062026125929_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1693377_15072026052102_WEB.xml</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>69464</t>
+          <t>70191</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>18-JUN-2026</t>
+          <t>14-JUL-2026</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>STERLITE TECHNOLOGIES LIMITED</t>
+          <t>BELRISE INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>L31300PN2000PLC202408</t>
+          <t>L73100MH1996PLC102827</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>29-APR-2026</t>
+          <t>24-MAY-2026</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>16-JUN-2026</t>
+          <t>30-JUN-2026</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>18-JUN-2026</t>
+          <t>14-JUL-2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>INE089C01029</t>
+          <t>INE894V01022</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3398,12 +3378,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>NSE,BSE</t>
+          <t>BSE,NSE</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>BELRISE</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3418,64 +3398,64 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>15000000000</t>
+          <t>19000000000</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>6.96 KB</t>
+          <t>7.25 KB</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1682458_18062026032420_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1692344_14072026045244_WEB.xml</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>69384</t>
+          <t>69970</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16-JUN-2026</t>
+          <t>06-JUL-2026</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Krishna Institute of Medical Sciences Limited</t>
+          <t>Blue Jet Healthcare Limited</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>L55101TG1973PLC040558</t>
+          <t>L99999MH1968PLC014154</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>11-MAR-2026</t>
+          <t>25-MAY-2026</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>15-APR-2026</t>
+          <t>17-JUN-2026</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>16-JUN-2026</t>
+          <t>06-JUL-2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>INE967H01025</t>
+          <t>INE0KBH01020</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3485,12 +3465,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>NSE,BSE</t>
+          <t>BSE,NSE</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>KIMS</t>
+          <t>BLUEJET</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3505,64 +3485,64 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>15000000000</t>
+          <t>10000000000</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>7.42 KB</t>
+          <t>7.92 KB</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1681986_16062026022109_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1688379_06072026021522_WEB.xml</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>69344</t>
+          <t>69767</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15-JUN-2026</t>
+          <t>29-JUN-2026</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Craftsman Automation Limited</t>
+          <t>Manorama Industries Limited</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>L28991TZ1986PLC001816</t>
+          <t>L15142MH2005PLC243687</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>16-MAY-2026</t>
+          <t>12-MAR-2026</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>13-JUN-2026</t>
+          <t>19-APR-2026</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>15-JUN-2026</t>
+          <t>29-JUN-2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>INE00LO01017</t>
+          <t>INE00VM01036</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3577,7 +3557,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>CRAFTSMAN</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3592,64 +3572,64 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>20000000000</t>
+          <t>5000000000</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>5.65 KB</t>
+          <t>6.09 KB</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1681644_15062026102836_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1685961_29062026032813_WEB.xml</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>69172</t>
+          <t>69538</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>09-JUN-2026</t>
+          <t>22-JUN-2026</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MOTISONS JEWELLERS LIMITED</t>
+          <t>JSW INFRASTRUCTURE LIMITED</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>L36911RJ2011PLC035122</t>
+          <t>L45200MH2006PLC161268</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>06-MAR-2026</t>
+          <t>20-FEB-2026</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>25-APR-2026</t>
+          <t>23-MAR-2026</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>09-JUN-2026</t>
+          <t>22-JUN-2026</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>INE0FRK01020</t>
+          <t>INE880J01026</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3664,7 +3644,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>MOTISONS</t>
+          <t>JSWINFRA</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3679,64 +3659,64 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>1500000000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>4.81 KB</t>
+          <t>10.49 KB</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1680350_09062026094217_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1683149_22062026125929_WEB.xml</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>68933</t>
+          <t>69464</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01-JUN-2026</t>
+          <t>18-JUN-2026</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ola Electric Mobility Limited</t>
+          <t>STERLITE TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>L74999KA2017PLC099619</t>
+          <t>L31300PN2000PLC202408</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>25-OCT-2025</t>
+          <t>29-APR-2026</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>27-NOV-2025</t>
+          <t>16-JUN-2026</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>01-JUN-2026</t>
+          <t>18-JUN-2026</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>INE0LXG01040</t>
+          <t>INE089C01029</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3746,17 +3726,17 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>BSE,NSE</t>
+          <t>NSE,BSE</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>OLAELEC</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0.0005</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3766,64 +3746,64 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>13000000000</t>
+          <t>15000000000</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>6.71 KB</t>
+          <t>6.96 KB</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1678297_01062026083949_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1682458_18062026032420_WEB.xml</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>68928</t>
+          <t>69384</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01-JUN-2026</t>
+          <t>16-JUN-2026</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ACME SOLAR HOLDINGS LIMITED</t>
+          <t>Krishna Institute of Medical Sciences Limited</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>L40106HR2015PLC102129</t>
+          <t>L55101TG1973PLC040558</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>27-AUG-2025</t>
+          <t>11-MAR-2026</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>29-SEP-2025</t>
+          <t>15-APR-2026</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>01-JUN-2026</t>
+          <t>16-JUN-2026</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>INE622W01025</t>
+          <t>INE967H01025</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3838,7 +3818,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>ACMESOLAR</t>
+          <t>KIMS</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3853,64 +3833,64 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>30000000000</t>
+          <t>15000000000</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>6.96 KB</t>
+          <t>7.42 KB</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1678377_01062026023625_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1681986_16062026022109_WEB.xml</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>68846</t>
+          <t>69344</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>26-MAY-2026</t>
+          <t>15-JUN-2026</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>KRN HEAT EXCHANGER AND REFRIGERATION LIMITED</t>
+          <t>Craftsman Automation Limited</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>L29309RJ2017PLC058905</t>
+          <t>L28991TZ1986PLC001816</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>13-MAR-2025</t>
+          <t>16-MAY-2026</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>15-APR-2025</t>
+          <t>13-JUN-2026</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>26-MAY-2026</t>
+          <t>15-JUN-2026</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>INE0Q3J01015</t>
+          <t>INE00LO01017</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3920,12 +3900,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>NSE,BSE</t>
+          <t>BSE,NSE</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>CRAFTSMAN</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3940,64 +3920,64 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>3500000000</t>
+          <t>20000000000</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>7.17 KB</t>
+          <t>5.65 KB</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1673482_26052026080204_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1681644_15062026102836_WEB.xml</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>68683</t>
+          <t>69172</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20-MAY-2026</t>
+          <t>09-JUN-2026</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>JSW Energy Limited</t>
+          <t>MOTISONS JEWELLERS LIMITED</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>L74999MH1994PLC077041</t>
+          <t>L36911RJ2011PLC035122</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>12-DEC-2025</t>
+          <t>06-MAR-2026</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>03-JAN-2026</t>
+          <t>25-APR-2026</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20-MAY-2026</t>
+          <t>09-JUN-2026</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>INE121E01018</t>
+          <t>INE0FRK01020</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4012,7 +3992,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>MOTISONS</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4027,64 +4007,64 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>50000000000</t>
+          <t>1500000000</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>6.31 KB</t>
+          <t>4.81 KB</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1669900_20052026040842_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1680350_09062026094217_WEB.xml</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>69890</t>
+          <t>68933</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>30-APR-2026</t>
+          <t>01-JUN-2026</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ADANI ENTERPRISES LIMITED</t>
+          <t>Ola Electric Mobility Limited</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>L51100GJ1993PLC019067</t>
+          <t>L74999KA2017PLC099619</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>24-JUN-2026</t>
+          <t>25-OCT-2025</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>24-JUN-2026</t>
+          <t>27-NOV-2025</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>02-JUL-2026</t>
+          <t>01-JUN-2026</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>INE423A01024</t>
+          <t>INE0LXG01040</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4099,12 +4079,12 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>OLAELEC</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0005</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4114,64 +4094,64 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>150000000000</t>
+          <t>13000000000</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>8.71 KB</t>
+          <t>6.71 KB</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1687413_02072026092552_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1678297_01062026083949_WEB.xml</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>67719</t>
+          <t>68928</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>09-APR-2026</t>
+          <t>01-JUN-2026</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Poonawalla Fincorp Limited</t>
+          <t>ACME SOLAR HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>L51504PN1978PLC209007</t>
+          <t>L40106HR2015PLC102129</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>16-JAN-2026</t>
+          <t>27-AUG-2025</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>19-FEB-2026</t>
+          <t>29-SEP-2025</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>09-APR-2026</t>
+          <t>01-JUN-2026</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>INE511C01022</t>
+          <t>INE622W01025</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4181,12 +4161,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>BSE,NSE</t>
+          <t>NSE,BSE</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>POONAWALLA</t>
+          <t>ACMESOLAR</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4201,64 +4181,64 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>55000000000</t>
+          <t>30000000000</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>7.39 KB</t>
+          <t>6.96 KB</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1647814_09042026125441_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1678377_01062026023625_WEB.xml</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>66716</t>
+          <t>68846</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>02-MAR-2026</t>
+          <t>26-MAY-2026</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AGI INFRA LIMITED</t>
+          <t>KRN HEAT EXCHANGER AND REFRIGERATION LIMITED</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>L45200PB2005PLC028466</t>
+          <t>L29309RJ2017PLC058905</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>23-OCT-2025</t>
+          <t>13-MAR-2025</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>29-NOV-2025</t>
+          <t>15-APR-2025</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>02-MAR-2026</t>
+          <t>26-MAY-2026</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>INE976R01033</t>
+          <t>INE0Q3J01015</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4268,12 +4248,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>BSE,NSE</t>
+          <t>NSE,BSE</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>AGIIL</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4288,64 +4268,64 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>750000000</t>
+          <t>3500000000</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>6.41 KB</t>
+          <t>7.17 KB</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1631684_02032026032414_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1673482_26052026080204_WEB.xml</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>66590</t>
+          <t>68683</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>25-FEB-2026</t>
+          <t>20-MAY-2026</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>E2E Networks Limited</t>
+          <t>JSW Energy Limited</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>L72900DL2009PLC341980</t>
+          <t>L74999MH1994PLC077041</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>29-SEP-2025</t>
+          <t>12-DEC-2025</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>30-OCT-2025</t>
+          <t>03-JAN-2026</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>25-FEB-2026</t>
+          <t>20-MAY-2026</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>INE255Z01019</t>
+          <t>INE121E01018</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4355,12 +4335,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>NSE</t>
+          <t>BSE,NSE</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4375,64 +4355,64 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>1500000000</t>
+          <t>50000000000</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>5.76 KB</t>
+          <t>6.31 KB</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1630032_25022026060222_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1669900_20052026040842_WEB.xml</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>65432</t>
+          <t>69890</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>29-JAN-2026</t>
+          <t>30-APR-2026</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GACM TECHNOLOGIES LIMITED</t>
+          <t>ADANI ENTERPRISES LIMITED</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>L67120TG1995PLC020170</t>
+          <t>L51100GJ1993PLC019067</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>03-SEP-2025</t>
+          <t>24-JUN-2026</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>25-SEP-2025</t>
+          <t>24-JUN-2026</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>13-JAN-2026</t>
+          <t>02-JUL-2026</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>INE224E01028</t>
+          <t>INE423A01024</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4447,12 +4427,12 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>GATECH</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4462,60 +4442,64 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>495000000</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr"/>
+          <t>150000000000</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>8.71 KB</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1599445_13012026123327_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1687413_02072026092552_WEB.xml</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>65404</t>
+          <t>67719</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12-JAN-2026</t>
+          <t>09-APR-2026</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BIOCON LIMITED</t>
+          <t>Poonawalla Fincorp Limited</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>L24234KA1978PLC003417</t>
+          <t>L51504PN1978PLC209007</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>06-DEC-2025</t>
+          <t>16-JAN-2026</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>31-DEC-2025</t>
+          <t>19-FEB-2026</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>12-JAN-2026</t>
+          <t>09-APR-2026</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>INE376G01013</t>
+          <t>INE511C01022</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4530,7 +4514,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>BIOCON</t>
+          <t>POONAWALLA</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4545,60 +4529,64 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>45000000000</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr"/>
+          <t>55000000000</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>7.39 KB</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1598371_12012026105319_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1647814_09042026125441_WEB.xml</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>64841</t>
+          <t>66716</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>23-DEC-2025</t>
+          <t>02-MAR-2026</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Garuda Construction and Engineering Limited</t>
+          <t>AGI INFRA LIMITED</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>U45400MH2010PLC207963</t>
+          <t>L45200PB2005PLC028466</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>07-NOV-2025</t>
+          <t>23-OCT-2025</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>01-DEC-2025</t>
+          <t>29-NOV-2025</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>18-DEC-2025</t>
+          <t>02-MAR-2026</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>INE0JVO01026</t>
+          <t>INE976R01033</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4613,7 +4601,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>GARUDA</t>
+          <t>AGIIL</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4628,60 +4616,64 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>5000000000</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr"/>
+          <t>750000000</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>6.41 KB</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1587411_18122025083849_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1631684_02032026032414_WEB.xml</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>64889</t>
+          <t>66590</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>22-DEC-2025</t>
+          <t>25-FEB-2026</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>HFCL LIMITED</t>
+          <t>E2E Networks Limited</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>L64200HP1987PLC007466</t>
+          <t>L72900DL2009PLC341980</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>25-JUL-2025</t>
+          <t>29-SEP-2025</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>15-SEP-2025</t>
+          <t>30-OCT-2025</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>22-DEC-2025</t>
+          <t>25-FEB-2026</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>INE548A01028</t>
+          <t>INE255Z01019</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4691,12 +4683,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>NSE,BSE</t>
+          <t>NSE</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>E2E</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4711,60 +4703,64 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>6000000000</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr"/>
+          <t>1500000000</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>5.76 KB</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1588173_22122025122636_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1630032_25022026060222_WEB.xml</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>64692</t>
+          <t>65432</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15-DEC-2025</t>
+          <t>29-JAN-2026</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ZOTA HEALTH CARE LIMITED</t>
+          <t>GACM TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>L24231GJ2000PLC038352</t>
+          <t>L67120TG1995PLC020170</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>04-SEP-2025</t>
+          <t>03-SEP-2025</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>29-SEP-2025</t>
+          <t>25-SEP-2025</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>15-DEC-2025</t>
+          <t>13-JAN-2026</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>INE358U01012</t>
+          <t>INE224E01028</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4774,17 +4770,17 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>NSE</t>
+          <t>BSE,NSE</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>ZOTA</t>
+          <t>GATECH</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4794,60 +4790,60 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>4000000000</t>
+          <t>495000000</t>
         </is>
       </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1586111_15122025063352_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1599445_13012026123327_WEB.xml</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>64452</t>
+          <t>65404</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>09-DEC-2025</t>
+          <t>12-JAN-2026</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SWIGGY LIMITED</t>
+          <t>BIOCON LIMITED</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>L74110KA2013PLC096530</t>
+          <t>L24234KA1978PLC003417</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>07-NOV-2025</t>
+          <t>06-DEC-2025</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>08-DEC-2025</t>
+          <t>31-DEC-2025</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>09-DEC-2025</t>
+          <t>12-JAN-2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>INE00H001014</t>
+          <t>INE376G01013</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4857,12 +4853,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>NSE,BSE</t>
+          <t>BSE,NSE</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>SWIGGY</t>
+          <t>BIOCON</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4877,60 +4873,60 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>100000000000</t>
+          <t>45000000000</t>
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1584066_09122025114733_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1598371_12012026105319_WEB.xml</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>64191</t>
+          <t>64841</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>23-DEC-2025</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Garuda Construction and Engineering Limited</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>U45400MH2010PLC207963</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>07-NOV-2025</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t>01-DEC-2025</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>RATNAVEER PRECISION ENGINEERING LIMITED</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>L27108GJ2002PLC040488</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>06-JUN-2025</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>04-JUL-2025</t>
-        </is>
-      </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>01-DEC-2025</t>
+          <t>18-DEC-2025</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>INE05CZ01011</t>
+          <t>INE0JVO01026</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4945,7 +4941,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>RATNAVEER</t>
+          <t>GARUDA</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4960,60 +4956,60 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2110000000</t>
+          <t>5000000000</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1581537_01122025033046_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1587411_18122025083849_WEB.xml</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>63509</t>
+          <t>64889</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>06-NOV-2025</t>
+          <t>22-DEC-2025</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TIME TECHNOPLAST LIMITED</t>
+          <t>HFCL LIMITED</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>L27203DD1989PLC003240</t>
+          <t>L64200HP1987PLC007466</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>25-OCT-2024</t>
+          <t>25-JUL-2025</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>28-NOV-2024</t>
+          <t>15-SEP-2025</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>06-NOV-2025</t>
+          <t>22-DEC-2025</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>INE508G01029</t>
+          <t>INE548A01028</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5023,12 +5019,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>BSE,NSE</t>
+          <t>NSE,BSE</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>TIMETECHNO</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5043,60 +5039,60 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>8500000000</t>
+          <t>6000000000</t>
         </is>
       </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1566485_06112025010522_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1588173_22122025122636_WEB.xml</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>62952</t>
+          <t>64692</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>30-OCT-2025</t>
+          <t>15-DEC-2025</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>V2 Retail Limited</t>
+          <t>ZOTA HEALTH CARE LIMITED</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>L74999DL2001PLC147724</t>
+          <t>L24231GJ2000PLC038352</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>30-JUL-2025</t>
+          <t>04-SEP-2025</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>05-SEP-2025</t>
+          <t>29-SEP-2025</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>30-OCT-2025</t>
+          <t>15-DEC-2025</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>INE945H01013</t>
+          <t>INE358U01012</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5106,12 +5102,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>BSE,NSE</t>
+          <t>NSE</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>V2RETAIL</t>
+          <t>ZOTA</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5132,54 +5128,54 @@
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1561315_30102025033130_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1586111_15122025063352_WEB.xml</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>62663</t>
+          <t>64452</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>07-OCT-2025</t>
+          <t>09-DEC-2025</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ANANT RAJ LIMITED</t>
+          <t>SWIGGY LIMITED</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>L45400HR1985PLC021622</t>
+          <t>L74110KA2013PLC096530</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>28-OCT-2024</t>
+          <t>07-NOV-2025</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>03-DEC-2024</t>
+          <t>08-DEC-2025</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>07-OCT-2025</t>
+          <t>09-DEC-2025</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>INE242C01024</t>
+          <t>INE00H001014</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5189,12 +5185,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>BSE,NSE</t>
+          <t>NSE,BSE</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>ANANTRAJ</t>
+          <t>SWIGGY</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5209,60 +5205,60 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>11000000000</t>
+          <t>100000000000</t>
         </is>
       </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1542004_07102025051247_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1584066_09122025114733_WEB.xml</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>62051</t>
+          <t>64191</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>16-SEP-2025</t>
+          <t>01-DEC-2025</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AMBER ENTERPRISES INDIA LIMITED</t>
+          <t>RATNAVEER PRECISION ENGINEERING LIMITED</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>L28910PB1990PLC010265</t>
+          <t>L27108GJ2002PLC040488</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>12-JUL-2025</t>
+          <t>06-JUN-2025</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>11-AUG-2025</t>
+          <t>04-JUL-2025</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>16-SEP-2025</t>
+          <t>01-DEC-2025</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>INE371P01015</t>
+          <t>INE05CZ01011</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5277,7 +5273,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>RATNAVEER</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5292,60 +5288,60 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>12000000000</t>
+          <t>2110000000</t>
         </is>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1527615_16092025105624_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1581537_01122025033046_WEB.xml</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>62022</t>
+          <t>63509</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>15-SEP-2025</t>
+          <t>06-NOV-2025</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Asahi India Glass Limited</t>
+          <t>TIME TECHNOPLAST LIMITED</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>L26102DL1984PLC019542</t>
+          <t>L27203DD1989PLC003240</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>29-JAN-2025</t>
+          <t>25-OCT-2024</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>15-MAR-2025</t>
+          <t>28-NOV-2024</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>15-SEP-2025</t>
+          <t>06-NOV-2025</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>INE439A01020</t>
+          <t>INE508G01029</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5360,7 +5356,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>ASAHIINDIA</t>
+          <t>TIMETECHNO</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5375,60 +5371,60 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>10000000000</t>
+          <t>8500000000</t>
         </is>
       </c>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1527199_15092025030527_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1566485_06112025010522_WEB.xml</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>61821</t>
+          <t>62952</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>08-SEP-2025</t>
+          <t>30-OCT-2025</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BASILIC FLY STUDIO LIMITED</t>
+          <t>V2 Retail Limited</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>L92100TN2016PLC103861</t>
+          <t>L74999DL2001PLC147724</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>12-JUL-2025</t>
+          <t>30-JUL-2025</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>09-AUG-2025</t>
+          <t>05-SEP-2025</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>08-SEP-2025</t>
+          <t>30-OCT-2025</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>INE0OCC01013</t>
+          <t>INE945H01013</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5438,12 +5434,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>NSE</t>
+          <t>BSE,NSE</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>BASILIC</t>
+          <t>V2RETAIL</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5458,60 +5454,60 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>850000000</t>
+          <t>4000000000</t>
         </is>
       </c>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1524724_08092025012005_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1561315_30102025033130_WEB.xml</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>61069</t>
+          <t>62663</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>12-AUG-2025</t>
+          <t>07-OCT-2025</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Goldiam International Limited</t>
+          <t>ANANT RAJ LIMITED</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>L36912MH1986PLC041203</t>
+          <t>L45400HR1985PLC021622</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>07-MAY-2025</t>
+          <t>28-OCT-2024</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>08-JUN-2025</t>
+          <t>03-DEC-2024</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>12-AUG-2025</t>
+          <t>07-OCT-2025</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>INE025B01025</t>
+          <t>INE242C01024</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5526,7 +5522,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>GOLDIAM</t>
+          <t>ANANTRAJ</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5541,60 +5537,60 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2750000000</t>
+          <t>11000000000</t>
         </is>
       </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1509815_12082025053753_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1542004_07102025051247_WEB.xml</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>60944</t>
+          <t>62051</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>07-AUG-2025</t>
+          <t>16-SEP-2025</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Syrma SGS Technology Limited</t>
+          <t>AMBER ENTERPRISES INDIA LIMITED</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>L30007MH2004PLC148165</t>
+          <t>L28910PB1990PLC010265</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>10-MAY-2024</t>
+          <t>12-JUL-2025</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>17-SEP-2024</t>
+          <t>11-AUG-2025</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>07-AUG-2025</t>
+          <t>16-SEP-2025</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>INE0DYJ01015</t>
+          <t>INE371P01015</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5609,7 +5605,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5624,60 +5620,60 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>10000000000</t>
+          <t>12000000000</t>
         </is>
       </c>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1505268_07082025050432_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1527615_16092025105624_WEB.xml</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>60352</t>
+          <t>62022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>17-JUL-2025</t>
+          <t>15-SEP-2025</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Veranda Learning Solutions Limited</t>
+          <t>Asahi India Glass Limited</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>L74999TN2018PLC125880</t>
+          <t>L26102DL1984PLC019542</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>17-MAY-2025</t>
+          <t>29-JAN-2025</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>10-JUN-2025</t>
+          <t>15-MAR-2025</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>17-JUL-2025</t>
+          <t>15-SEP-2025</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>INE0IQ001011</t>
+          <t>INE439A01020</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5692,7 +5688,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>VERANDA</t>
+          <t>ASAHIINDIA</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5707,60 +5703,60 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>3800000000</t>
+          <t>10000000000</t>
         </is>
       </c>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1485334_17072025032626_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1527199_15092025030527_WEB.xml</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>60316</t>
+          <t>61821</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>16-JUL-2025</t>
+          <t>08-SEP-2025</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>STATE BANK OF INDIA</t>
+          <t>BASILIC FLY STUDIO LIMITED</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Z99999ZZ9999ZZZ999999</t>
+          <t>L92100TN2016PLC103861</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>03-MAY-2025</t>
+          <t>12-JUL-2025</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>13-JUN-2025</t>
+          <t>09-AUG-2025</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>16-JUL-2025</t>
+          <t>08-SEP-2025</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>INE062A01020</t>
+          <t>INE0OCC01013</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5770,12 +5766,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>BSE,NSE</t>
+          <t>NSE</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>BASILIC</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5790,60 +5786,60 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>250000000000</t>
+          <t>850000000</t>
         </is>
       </c>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1483794_16072025111129_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1524724_08092025012005_WEB.xml</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>60278</t>
+          <t>61069</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15-JUL-2025</t>
+          <t>12-AUG-2025</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>U. Y. FINCORP LIMITED</t>
+          <t>Goldiam International Limited</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>L65993WB1993PLC060377</t>
+          <t>L36912MH1986PLC041203</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>14-FEB-2025</t>
+          <t>07-MAY-2025</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>25-MAR-2025</t>
+          <t>08-JUN-2025</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>15-JUL-2025</t>
+          <t>12-AUG-2025</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>INE152C01025</t>
+          <t>INE025B01025</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5853,12 +5849,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>NSE,BSE</t>
+          <t>BSE,NSE</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>GOLDIAM</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5873,60 +5869,60 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>500000000</t>
+          <t>2750000000</t>
         </is>
       </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1482766_15072025114123_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1509815_12082025053753_WEB.xml</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>60080</t>
+          <t>60944</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>08-JUL-2025</t>
+          <t>07-AUG-2025</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>PHANTOM DIGITAL EFFECTS LIMITED</t>
+          <t>Syrma SGS Technology Limited</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>L92100TN2016PLC103929</t>
+          <t>L30007MH2004PLC148165</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>03-MAR-2025</t>
+          <t>10-MAY-2024</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>26-MAR-2025</t>
+          <t>17-SEP-2024</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>07-JUL-2025</t>
+          <t>07-AUG-2025</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>INE0MLZ01019</t>
+          <t>INE0DYJ01015</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -5936,12 +5932,12 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>NSE</t>
+          <t>BSE,NSE</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>PHANTOMFX</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5956,60 +5952,60 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>600000000</t>
+          <t>10000000000</t>
         </is>
       </c>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1478035_07072025022030_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1505268_07082025050432_WEB.xml</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>60083</t>
+          <t>60352</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>07-JUL-2025</t>
+          <t>17-JUL-2025</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NAVIN FLUORINE INTERNATIONAL LIMITED</t>
+          <t>Veranda Learning Solutions Limited</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>L24110MH1998PLC115499</t>
+          <t>L74999TN2018PLC125880</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>29-JUN-2024</t>
+          <t>17-MAY-2025</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>01-AUG-2024</t>
+          <t>10-JUN-2025</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>07-JUL-2025</t>
+          <t>17-JUL-2025</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>INE048G01026</t>
+          <t>INE0IQ001011</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6024,7 +6020,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>VERANDA</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6039,60 +6035,60 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>7500000000</t>
+          <t>3800000000</t>
         </is>
       </c>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1478023_07072025020407_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1485334_17072025032626_WEB.xml</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>59949</t>
+          <t>60316</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>02-JUL-2025</t>
+          <t>16-JUL-2025</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SHAKTI PUMPS (INDIA) LIMITED</t>
+          <t>STATE BANK OF INDIA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>L29120MP1995PLC009327</t>
+          <t>Z99999ZZ9999ZZZ999999</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>07-JAN-2025</t>
+          <t>03-MAY-2025</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>12-FEB-2025</t>
+          <t>13-JUN-2025</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>02-JUL-2025</t>
+          <t>16-JUL-2025</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>INE908D01010</t>
+          <t>INE062A01020</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6102,12 +6098,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>NSE,BSE</t>
+          <t>BSE,NSE</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6122,60 +6118,60 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>4000000000</t>
+          <t>250000000000</t>
         </is>
       </c>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1476540_02072025063600_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1483794_16072025111129_WEB.xml</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>59887</t>
+          <t>60278</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>30-JUN-2025</t>
+          <t>15-JUL-2025</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>HOAC FOODS INDIA LIMITED</t>
+          <t>U. Y. FINCORP LIMITED</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>L15120DL2018PLC330739</t>
+          <t>L65993WB1993PLC060377</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>29-MAY-2025</t>
+          <t>14-FEB-2025</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>26-JUN-2025</t>
+          <t>25-MAR-2025</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>30-JUN-2025</t>
+          <t>15-JUL-2025</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>INE0S6S01017</t>
+          <t>INE152C01025</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6185,12 +6181,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>NSE</t>
+          <t>NSE,BSE</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>HOACFOODS</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6205,60 +6201,60 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>100000000</t>
+          <t>500000000</t>
         </is>
       </c>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1474922_30062025054401_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1482766_15072025114123_WEB.xml</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>59886</t>
+          <t>60080</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>30-JUN-2025</t>
+          <t>08-JUL-2025</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CG Power and Industrial Solutions Limited</t>
+          <t>PHANTOM DIGITAL EFFECTS LIMITED</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>L99999MH1937PLC002641</t>
+          <t>L92100TN2016PLC103929</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>21-OCT-2024</t>
+          <t>03-MAR-2025</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>18-DEC-2025</t>
+          <t>26-MAR-2025</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>30-JUN-2025</t>
+          <t>07-JUL-2025</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>INE067A01029</t>
+          <t>INE0MLZ01019</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6268,12 +6264,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>BSE,NSE</t>
+          <t>NSE</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>PHANTOMFX</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6288,60 +6284,60 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>30000000000</t>
+          <t>600000000</t>
         </is>
       </c>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1474708_30062025043014_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1478035_07072025022030_WEB.xml</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>59703</t>
+          <t>60083</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>24-JUN-2025</t>
+          <t>07-JUL-2025</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>TINNA RUBBER AND INFRASTRUCTURE LIMITED</t>
+          <t>NAVIN FLUORINE INTERNATIONAL LIMITED</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>L51909DL1987PLC027186</t>
+          <t>L24110MH1998PLC115499</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>08-FEB-2025</t>
+          <t>29-JUN-2024</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>14-MAR-2025</t>
+          <t>01-AUG-2024</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>24-JUN-2025</t>
+          <t>07-JUL-2025</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>INE015C01016</t>
+          <t>INE048G01026</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6356,7 +6352,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>TINNARUBR</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -6371,60 +6367,60 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>1000000000</t>
+          <t>7500000000</t>
         </is>
       </c>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1470483_24062025060947_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1478023_07072025020407_WEB.xml</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>59685</t>
+          <t>59949</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>23-JUN-2025</t>
+          <t>02-JUL-2025</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MARATHON NEXTGEN REALTY LIMITED</t>
+          <t>SHAKTI PUMPS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>L65990MH1978PLC020080</t>
+          <t>L29120MP1995PLC009327</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>11-NOV-2024</t>
+          <t>07-JAN-2025</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>14-DEC-2024</t>
+          <t>12-FEB-2025</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>23-JUN-2025</t>
+          <t>02-JUL-2025</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>INE182D01020</t>
+          <t>INE908D01010</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6434,12 +6430,12 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>BSE,NSE</t>
+          <t>NSE,BSE</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>MARATHON</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -6454,60 +6450,60 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>9000000000</t>
+          <t>4000000000</t>
         </is>
       </c>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1469928_23062025075321_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1476540_02072025063600_WEB.xml</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>59570</t>
+          <t>59887</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>19-JUN-2025</t>
+          <t>30-JUN-2025</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Kaynes Technology India Limited</t>
+          <t>HOAC FOODS INDIA LIMITED</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>L29128KA2008PLC045825</t>
+          <t>L15120DL2018PLC330739</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>22-JAN-2025</t>
+          <t>29-MAY-2025</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>14-FEB-2025</t>
+          <t>26-JUN-2025</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>19-JUN-2025</t>
+          <t>30-JUN-2025</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>INE918Z01012</t>
+          <t>INE0S6S01017</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6517,12 +6513,12 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>NSE,BSE</t>
+          <t>NSE</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>KAYNES</t>
+          <t>HOACFOODS</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -6537,60 +6533,60 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>16000000000</t>
+          <t>100000000</t>
         </is>
       </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1468403_19062025030229_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1474922_30062025054401_WEB.xml</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>59432</t>
+          <t>59886</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>16-JUN-2025</t>
+          <t>30-JUN-2025</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BIOCON LIMITED</t>
+          <t>CG Power and Industrial Solutions Limited</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>L24234KA1978PLC003417</t>
+          <t>L99999MH1937PLC002641</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>23-APR-2025</t>
+          <t>21-OCT-2024</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>04-JUN-2025</t>
+          <t>18-DEC-2025</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>16-JUN-2025</t>
+          <t>30-JUN-2025</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>INE376G01013</t>
+          <t>INE067A01029</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6605,7 +6601,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>BIOCON</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -6620,60 +6616,60 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>45000000000</t>
+          <t>30000000000</t>
         </is>
       </c>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1466939_16062025014654_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1474708_30062025043014_WEB.xml</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>59242</t>
+          <t>59703</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>09-JUN-2025</t>
+          <t>24-JUN-2025</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Capri Global Capital Limited</t>
+          <t>TINNA RUBBER AND INFRASTRUCTURE LIMITED</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>L65921MH1994PLC173469</t>
+          <t>L51909DL1987PLC027186</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>03-AUG-2024</t>
+          <t>08-FEB-2025</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>19-SEP-2024</t>
+          <t>14-MAR-2025</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>09-JUN-2025</t>
+          <t>24-JUN-2025</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>INE180C01042</t>
+          <t>INE015C01016</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6688,7 +6684,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>TINNARUBR</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6703,60 +6699,60 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>20000000000</t>
+          <t>1000000000</t>
         </is>
       </c>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1464506_09062025014742_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1470483_24062025060947_WEB.xml</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>59046</t>
+          <t>59685</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>05-JUN-2025</t>
+          <t>23-JUN-2025</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Indian Renewable Energy Development Agency Limited</t>
+          <t>MARATHON NEXTGEN REALTY LIMITED</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>L65100DL1987GOI027265</t>
+          <t>L65990MH1978PLC020080</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>23-JAN-2025</t>
+          <t>11-NOV-2024</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>24-FEB-2025</t>
+          <t>14-DEC-2024</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>05-JUN-2025</t>
+          <t>23-JUN-2025</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>INE202E01016</t>
+          <t>INE182D01020</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6771,7 +6767,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>IREDA</t>
+          <t>MARATHON</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -6786,60 +6782,60 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>50000000000</t>
+          <t>9000000000</t>
         </is>
       </c>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1463395_05062025051245_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1469928_23062025075321_WEB.xml</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>58523</t>
+          <t>59570</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>14-MAY-2025</t>
+          <t>19-JUN-2025</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Genesys International Corporation Limtied</t>
+          <t>Kaynes Technology India Limited</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>L65990MH1983PLC029197</t>
+          <t>L29128KA2008PLC045825</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
+          <t>22-JAN-2025</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t>14-FEB-2025</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>12-MAR-2025</t>
-        </is>
-      </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>14-MAY-2025</t>
+          <t>19-JUN-2025</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>INE727B01026</t>
+          <t>INE918Z01012</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -6854,7 +6850,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>GENESYS</t>
+          <t>KAYNES</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6869,60 +6865,60 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>1200000000</t>
+          <t>16000000000</t>
         </is>
       </c>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1438907_14052025071509_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1468403_19062025030229_WEB.xml</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>58014</t>
+          <t>59432</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
+          <t>16-JUN-2025</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>BIOCON LIMITED</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>L24234KA1978PLC003417</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
           <t>23-APR-2025</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>PHANTOM DIGITAL EFFECTS LIMITED</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>L92100TN2016PLC103929</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>03-MAR-2025</t>
-        </is>
-      </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>26-MAR-2025</t>
+          <t>04-JUN-2025</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>22-APR-2025</t>
+          <t>16-JUN-2025</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>INE0MLZ01019</t>
+          <t>INE376G01013</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -6932,12 +6928,12 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>NSE</t>
+          <t>BSE,NSE</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>PHANTOMFX</t>
+          <t>BIOCON</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6952,60 +6948,60 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>800000000</t>
+          <t>45000000000</t>
         </is>
       </c>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1423040_23042025015025_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1466939_16062025014654_WEB.xml</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>57981</t>
+          <t>59242</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>21-APR-2025</t>
+          <t>09-JUN-2025</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>KAY CEE ENERGY &amp; INFRA LIMITED</t>
+          <t>Capri Global Capital Limited</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>U74900RJ2015PLC046976</t>
+          <t>L65921MH1994PLC173469</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>28-JAN-2025</t>
+          <t>03-AUG-2024</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>27-FEB-2025</t>
+          <t>19-SEP-2024</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>21-APR-2025</t>
+          <t>09-JUN-2025</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>INE0RCG01017</t>
+          <t>INE180C01042</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7015,12 +7011,12 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>NSE</t>
+          <t>BSE,NSE</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>KAYCEE</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -7035,60 +7031,60 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>250000000</t>
+          <t>20000000000</t>
         </is>
       </c>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1420915_21042025020453_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1464506_09062025014742_WEB.xml</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>57778</t>
+          <t>59046</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>08-APR-2025</t>
+          <t>05-JUN-2025</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Home First Finance Company India Limited</t>
+          <t>Indian Renewable Energy Development Agency Limited</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>L65990MH2010PLC240703</t>
+          <t>L65100DL1987GOI027265</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>28-JAN-2025</t>
+          <t>23-JAN-2025</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>13-MAR-2025</t>
+          <t>24-FEB-2025</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>08-APR-2025</t>
+          <t>05-JUN-2025</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>INE481N01025</t>
+          <t>INE202E01016</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7103,7 +7099,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>HOMEFIRST</t>
+          <t>IREDA</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -7118,60 +7114,60 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>12500000000</t>
+          <t>50000000000</t>
         </is>
       </c>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1409974_08042025030916_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1463395_05062025051245_WEB.xml</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>57376</t>
+          <t>58523</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>24-MAR-2025</t>
+          <t>14-MAY-2025</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>UCOBANK</t>
+          <t>Genesys International Corporation Limtied</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Z99999ZZ9999ZZZ999999</t>
+          <t>L65990MH1983PLC029197</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>29-APR-2024</t>
+          <t>14-FEB-2025</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>18-JUN-2024</t>
+          <t>12-MAR-2025</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>24-MAR-2025</t>
+          <t>14-MAY-2025</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>INE691A01018</t>
+          <t>INE727B01026</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7181,12 +7177,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>BSE,NSE</t>
+          <t>NSE,BSE</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>UCOBANK</t>
+          <t>GENESYS</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -7201,60 +7197,60 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>20000000000</t>
+          <t>1200000000</t>
         </is>
       </c>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1400135_24032025024217_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1438907_14052025071509_WEB.xml</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>57377</t>
+          <t>58014</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>24-MAR-2025</t>
+          <t>23-APR-2025</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>RESTAURANT BRANDS ASIA LIMITED</t>
+          <t>PHANTOM DIGITAL EFFECTS LIMITED</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>L55204MH2013FLC249986</t>
+          <t>L92100TN2016PLC103929</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>20-DEC-2024</t>
+          <t>03-MAR-2025</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>25-JAN-2025</t>
+          <t>26-MAR-2025</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>24-MAR-2025</t>
+          <t>22-APR-2025</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>INE07T201019</t>
+          <t>INE0MLZ01019</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7264,12 +7260,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>NSE,BSE</t>
+          <t>NSE</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>PHANTOMFX</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -7284,60 +7280,60 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>5000000000</t>
+          <t>800000000</t>
         </is>
       </c>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1399902_24032025100326_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1423040_23042025015025_WEB.xml</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>57386</t>
+          <t>57981</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>24-MAR-2025</t>
+          <t>21-APR-2025</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Punjab &amp; Sind Bank</t>
+          <t>KAY CEE ENERGY &amp; INFRA LIMITED</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Z99999ZZ9999ZZZ999999</t>
+          <t>U74900RJ2015PLC046976</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>28-FEB-2024</t>
+          <t>28-JAN-2025</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>31-MAY-2024</t>
+          <t>27-FEB-2025</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>24-MAR-2025</t>
+          <t>21-APR-2025</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>INE608A01012</t>
+          <t>INE0RCG01017</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7347,12 +7343,12 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>BSE,NSE</t>
+          <t>NSE</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>KAYCEE</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -7367,60 +7363,60 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>16000000000</t>
+          <t>250000000</t>
         </is>
       </c>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1400499_24032025060255_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1420915_21042025020453_WEB.xml</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>57387</t>
+          <t>57778</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>24-MAR-2025</t>
+          <t>08-APR-2025</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CENTRAL BANK OF INDIA</t>
+          <t>Home First Finance Company India Limited</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Z99999ZZ9999ZZZ999999</t>
+          <t>L65990MH2010PLC240703</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>30-APR-2024</t>
+          <t>28-JAN-2025</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>16-JUL-2024</t>
+          <t>13-MAR-2025</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>24-MAR-2025</t>
+          <t>08-APR-2025</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>INE483A01010</t>
+          <t>INE481N01025</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -7435,7 +7431,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>CENTRALBK</t>
+          <t>HOMEFIRST</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -7450,60 +7446,60 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>20000000000</t>
+          <t>12500000000</t>
         </is>
       </c>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1400245_24032025035734_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1409974_08042025030916_WEB.xml</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>57271</t>
+          <t>57377</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>19-MAR-2025</t>
+          <t>24-MAR-2025</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Indian Overseas Bank</t>
+          <t>RESTAURANT BRANDS ASIA LIMITED</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Z99999ZZ9999ZZZ999999</t>
+          <t>L55204MH2013FLC249986</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>22-APR-2024</t>
+          <t>20-DEC-2024</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>02-JUL-2024</t>
+          <t>25-JAN-2025</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>19-MAR-2025</t>
+          <t>24-MAR-2025</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>INE565A01014</t>
+          <t>INE07T201019</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -7518,7 +7514,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>NOTLISTED</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -7533,60 +7529,60 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>20000000000</t>
+          <t>5000000000</t>
         </is>
       </c>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1397984_19032025081712_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1399902_24032025100326_WEB.xml</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>57039</t>
+          <t>57387</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>10-MAR-2025</t>
+          <t>24-MAR-2025</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HITACHI ENERGY INDIA LIMITED</t>
+          <t>CENTRAL BANK OF INDIA</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>L31904KA2019PLC121597</t>
+          <t>Z99999ZZ9999ZZZ999999</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>18-JAN-2025</t>
+          <t>30-APR-2024</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>20-FEB-2025</t>
+          <t>16-JUL-2024</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>10-MAR-2025</t>
+          <t>24-MAR-2025</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>INE07Y701011</t>
+          <t>INE483A01010</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -7601,7 +7597,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>POWERINDIA</t>
+          <t>CENTRALBK</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -7616,60 +7612,60 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>35000000000</t>
+          <t>20000000000</t>
         </is>
       </c>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1394214_10032025012231_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1400245_24032025035734_WEB.xml</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>57031</t>
+          <t>57386</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>10-MAR-2025</t>
+          <t>24-MAR-2025</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CENTUM ELECTRONICS LIMITED</t>
+          <t>Punjab &amp; Sind Bank</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>L85110KA1993PLC013869</t>
+          <t>Z99999ZZ9999ZZZ999999</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>12-NOV-2024</t>
+          <t>28-FEB-2024</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>14-JAN-2025</t>
+          <t>31-MAY-2024</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>10-MAR-2025</t>
+          <t>24-MAR-2025</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>INE320B01020</t>
+          <t>INE608A01012</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7684,7 +7680,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>CENTUM</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -7699,60 +7695,60 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2500000000</t>
+          <t>16000000000</t>
         </is>
       </c>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1394313_10032025034918_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1400499_24032025060255_WEB.xml</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>56688</t>
+          <t>57376</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>25-FEB-2025</t>
+          <t>24-MAR-2025</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AZAD ENGINEERING LIMITED</t>
+          <t>UCOBANK</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>U74210TG1983PLC004132</t>
+          <t>Z99999ZZ9999ZZZ999999</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>03-JAN-2025</t>
+          <t>29-APR-2024</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>28-JAN-2025</t>
+          <t>18-JUN-2024</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>25-FEB-2025</t>
+          <t>24-MAR-2025</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>INE021J01035</t>
+          <t>INE691A01018</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7762,12 +7758,12 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>NSE,BSE</t>
+          <t>BSE,NSE</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>UCOBANK</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -7782,60 +7778,60 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>7000000000</t>
+          <t>20000000000</t>
         </is>
       </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1389842_25022025072806_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1400135_24032025024217_WEB.xml</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>55882</t>
+          <t>57271</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>23-JAN-2025</t>
+          <t>19-MAR-2025</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SUDARSHAN CHEMICAL INDUSTRIES LIMITED</t>
+          <t>Indian Overseas Bank</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>L24119PN1951PLC008409</t>
+          <t>Z99999ZZ9999ZZZ999999</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>16-OCT-2024</t>
+          <t>22-APR-2024</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>30-NOV-2024</t>
+          <t>02-JUL-2024</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>23-JAN-2025</t>
+          <t>19-MAR-2025</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>INE659A01023</t>
+          <t>INE565A01014</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -7845,12 +7841,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>BSE,NSE</t>
+          <t>NSE,BSE</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>SUDARSCHEM</t>
+          <t>NOTLISTED</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -7865,60 +7861,60 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>8000000000</t>
+          <t>20000000000</t>
         </is>
       </c>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1359419_23012025053238_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1397984_19032025081712_WEB.xml</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>55860</t>
+          <t>57039</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>22-JAN-2025</t>
+          <t>10-MAR-2025</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sammaan Capital Limited</t>
+          <t>HITACHI ENERGY INDIA LIMITED</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>U65923DL2006PLC150632</t>
+          <t>L31904KA2019PLC121597</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>11-DEC-2024</t>
+          <t>18-JAN-2025</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>03-JAN-2025</t>
+          <t>20-FEB-2025</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>02-JAN-2025</t>
+          <t>10-MAR-2025</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>INE148I01020</t>
+          <t>INE07Y701011</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -7926,10 +7922,14 @@
           <t>QIP</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr"/>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>BSE,NSE</t>
+        </is>
+      </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>SAMMAANCAP</t>
+          <t>POWERINDIA</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -7942,58 +7942,62 @@
           <t>In-Principle</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>35000000000</t>
+        </is>
+      </c>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1357236_22012025055824_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1394214_10032025012231_WEB.xml</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>55680</t>
+          <t>57031</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>15-JAN-2025</t>
+          <t>10-MAR-2025</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Aditya Birla Fashion and Retail Limited</t>
+          <t>CENTUM ELECTRONICS LIMITED</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>L18101MH2007PLC233901</t>
+          <t>L85110KA1993PLC013869</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>15-JAN-2025</t>
+          <t>12-NOV-2024</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>19-SEP-2024</t>
+          <t>14-JAN-2025</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>15-JAN-2025</t>
+          <t>10-MAR-2025</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>INE647O01011</t>
+          <t>INE320B01020</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8008,12 +8012,12 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>ABFRL</t>
+          <t>CENTUM</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -8023,60 +8027,60 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>25000000000</t>
+          <t>2500000000</t>
         </is>
       </c>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1345799_15012025012712_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1394313_10032025034918_WEB.xml</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>54940</t>
+          <t>56688</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>18-DEC-2024</t>
+          <t>25-FEB-2025</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>YATHARTH HOSPITAL &amp; TRAUMA CARE SERVICES LIMITED</t>
+          <t>AZAD ENGINEERING LIMITED</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>L85110DL2008PLC174706</t>
+          <t>U74210TG1983PLC004132</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>07-NOV-2024</t>
+          <t>03-JAN-2025</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>06-DEC-2024</t>
+          <t>28-JAN-2025</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>18-DEC-2024</t>
+          <t>25-FEB-2025</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>INE0JO301016</t>
+          <t>INE021J01035</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8091,7 +8095,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -8112,54 +8116,54 @@
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1328240_18122024104507_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1389842_25022025072806_WEB.xml</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>54950</t>
+          <t>55882</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>18-DEC-2024</t>
+          <t>23-JAN-2025</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Zaggle Prepaid Ocean Services Limited</t>
+          <t>SUDARSHAN CHEMICAL INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>L65999TG2011PLC074795</t>
+          <t>L24119PN1951PLC008409</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>30-OCT-2024</t>
+          <t>16-OCT-2024</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>02-DEC-2024</t>
+          <t>30-NOV-2024</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>18-DEC-2024</t>
+          <t>23-JAN-2025</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>INE07K301024</t>
+          <t>INE659A01023</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -8169,12 +8173,12 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>NSE,BSE</t>
+          <t>BSE,NSE</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>ZAGGLE</t>
+          <t>SUDARSCHEM</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -8189,60 +8193,60 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>9500000000</t>
+          <t>8000000000</t>
         </is>
       </c>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1328496_18122024043006_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1359419_23012025053238_WEB.xml</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>54910</t>
+          <t>55860</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>17-DEC-2024</t>
+          <t>22-JAN-2025</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Pondy Oxides and Chemicals Limited</t>
+          <t>Sammaan Capital Limited</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>L24294TN1995PLC030586</t>
+          <t>U65923DL2006PLC150632</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>23-SEP-2024</t>
+          <t>11-DEC-2024</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>25-OCT-2024</t>
+          <t>03-JAN-2025</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>17-DEC-2024</t>
+          <t>02-JAN-2025</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>INE063E01053</t>
+          <t>INE148I01020</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -8250,14 +8254,10 @@
           <t>QIP</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>BSE,NSE</t>
-        </is>
-      </c>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>POCL</t>
+          <t>SAMMAANCAP</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -8270,62 +8270,58 @@
           <t>In-Principle</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>1750000000</t>
-        </is>
-      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1328040_17122024050243_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1357236_22012025055824_WEB.xml</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>54860</t>
+          <t>55680</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>16-DEC-2024</t>
+          <t>15-JAN-2025</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>GRAVITA INDIA LIMITED</t>
+          <t>Aditya Birla Fashion and Retail Limited</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>L29308RJ1992PLC006870</t>
+          <t>L18101MH2007PLC233901</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>04-OCT-2024</t>
+          <t>15-JAN-2025</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>22-NOV-2024</t>
+          <t>19-SEP-2024</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>16-DEC-2024</t>
+          <t>15-JAN-2025</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>INE024L01027</t>
+          <t>INE647O01011</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -8340,12 +8336,12 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>GRAVITA</t>
+          <t>ABFRL</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -8355,60 +8351,60 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>10000000000</t>
+          <t>25000000000</t>
         </is>
       </c>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1327226_16122024010127_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1345799_15012025012712_WEB.xml</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>54869</t>
+          <t>54940</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>16-DEC-2024</t>
+          <t>18-DEC-2024</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>HINDUSTAN CONSTRUCTION COMPANY LIMITED</t>
+          <t>YATHARTH HOSPITAL &amp; TRAUMA CARE SERVICES LIMITED</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>L45200MH1926PLC001228</t>
+          <t>L85110DL2008PLC174706</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>05-AUG-2024</t>
+          <t>07-NOV-2024</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>17-SEP-2024</t>
+          <t>06-DEC-2024</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>16-DEC-2024</t>
+          <t>18-DEC-2024</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>INE549A01026</t>
+          <t>INE0JO301016</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -8418,12 +8414,12 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>NSE</t>
+          <t>NSE,BSE</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -8438,60 +8434,60 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>10000000000</t>
+          <t>7000000000</t>
         </is>
       </c>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1327436_16122024045433_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1328240_18122024104507_WEB.xml</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>54864</t>
+          <t>54950</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>16-DEC-2024</t>
+          <t>18-DEC-2024</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MANKIND PHARMA LIMITED</t>
+          <t>Zaggle Prepaid Ocean Services Limited</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>L74899DL1991PLC044843</t>
+          <t>L65999TG2011PLC074795</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>15-MAY-2024</t>
+          <t>30-OCT-2024</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>17-JUN-2024</t>
+          <t>02-DEC-2024</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>16-DEC-2024</t>
+          <t>18-DEC-2024</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>INE634S01028</t>
+          <t>INE07K301024</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -8501,12 +8497,12 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>BSE,NSE</t>
+          <t>NSE,BSE</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>ZAGGLE</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -8521,60 +8517,60 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>30000000000</t>
+          <t>9500000000</t>
         </is>
       </c>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1327313_16122024032246_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1328496_18122024043006_WEB.xml</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>54783</t>
+          <t>54910</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>12-DEC-2024</t>
+          <t>17-DEC-2024</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>KALPATARU PROJECTS INTERNATIONAL LIMITED</t>
+          <t>Pondy Oxides and Chemicals Limited</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>L40100GJ1981PLC004281</t>
+          <t>L24294TN1995PLC030586</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>28-OCT-2024</t>
+          <t>23-SEP-2024</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>30-NOV-2024</t>
+          <t>25-OCT-2024</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>12-DEC-2024</t>
+          <t>17-DEC-2024</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>INE220B01022</t>
+          <t>INE063E01053</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -8589,7 +8585,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>KPIL</t>
+          <t>POCL</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -8604,60 +8600,60 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>10000000000</t>
+          <t>1750000000</t>
         </is>
       </c>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1325796_12122024025042_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1328040_17122024050243_WEB.xml</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>54556</t>
+          <t>54860</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>04-DEC-2024</t>
+          <t>16-DEC-2024</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PG ELECTROPLAST LIMITED</t>
+          <t>GRAVITA INDIA LIMITED</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>L32109DL2003PLC119416</t>
+          <t>L29308RJ1992PLC006870</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>19-OCT-2024</t>
+          <t>04-OCT-2024</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>13-NOV-2024</t>
+          <t>22-NOV-2024</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>04-DEC-2024</t>
+          <t>16-DEC-2024</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>INE457L01029</t>
+          <t>INE024L01027</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -8672,7 +8668,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>GRAVITA</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -8687,60 +8683,60 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>15000000000</t>
+          <t>10000000000</t>
         </is>
       </c>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1322801_04122024011555_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1327226_16122024010127_WEB.xml</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>54536</t>
+          <t>54869</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>04-DEC-2024</t>
+          <t>16-DEC-2024</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bharat Forge Limited</t>
+          <t>HINDUSTAN CONSTRUCTION COMPANY LIMITED</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>L25209PN1961PLC012046</t>
+          <t>L45200MH1926PLC001228</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>08-AUG-2024</t>
+          <t>05-AUG-2024</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>08-NOV-2024</t>
+          <t>17-SEP-2024</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>04-DEC-2024</t>
+          <t>16-DEC-2024</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>INE465A01025</t>
+          <t>INE549A01026</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -8750,12 +8746,12 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>NSE,BSE</t>
+          <t>NSE</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -8770,60 +8766,60 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>20000000000</t>
+          <t>10000000000</t>
         </is>
       </c>
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1322769_04122024123600_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1327436_16122024045433_WEB.xml</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>54543</t>
+          <t>54864</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>03-DEC-2024</t>
+          <t>16-DEC-2024</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Wonderla Holidays Limited</t>
+          <t>MANKIND PHARMA LIMITED</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>L55101KA2002PLC031224</t>
+          <t>L74899DL1991PLC044843</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>04-OCT-2024</t>
+          <t>15-MAY-2024</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>09-NOV-2024</t>
+          <t>17-JUN-2024</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>03-DEC-2024</t>
+          <t>16-DEC-2024</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>INE066O01014</t>
+          <t>INE634S01028</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -8838,7 +8834,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>WONDERLA</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -8853,60 +8849,60 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>6000000000</t>
+          <t>30000000000</t>
         </is>
       </c>
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1322614_03122024065148_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1327313_16122024032246_WEB.xml</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>54480</t>
+          <t>54783</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>02-DEC-2024</t>
+          <t>12-DEC-2024</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Torrent Power Limited</t>
+          <t>KALPATARU PROJECTS INTERNATIONAL LIMITED</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>L31200GJ2004PLC044068</t>
+          <t>L40100GJ1981PLC004281</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>22-MAY-2024</t>
+          <t>28-OCT-2024</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>30-JUL-2024</t>
+          <t>30-NOV-2024</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>02-DEC-2024</t>
+          <t>12-DEC-2024</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>INE813H01021</t>
+          <t>INE220B01022</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -8921,7 +8917,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>KPIL</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -8936,60 +8932,60 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>50000000000</t>
+          <t>10000000000</t>
         </is>
       </c>
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1321780_02122024124744_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1325796_12122024025042_WEB.xml</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>54261</t>
+          <t>54556</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>25-NOV-2024</t>
+          <t>04-DEC-2024</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>KEI Industries Limited</t>
+          <t>PG ELECTROPLAST LIMITED</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>L74899DL1992PLC051527</t>
+          <t>L32109DL2003PLC119416</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>15-OCT-2024</t>
+          <t>19-OCT-2024</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>17-NOV-2024</t>
+          <t>13-NOV-2024</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>25-NOV-2024</t>
+          <t>04-DEC-2024</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>INE878B01027</t>
+          <t>INE457L01029</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -9004,7 +9000,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>KEI</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -9019,60 +9015,60 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>20000000000</t>
+          <t>15000000000</t>
         </is>
       </c>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1319116_25112024050652_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1322801_04122024011555_WEB.xml</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>54258</t>
+          <t>54536</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>25-NOV-2024</t>
+          <t>04-DEC-2024</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ZOMATO LIMITED</t>
+          <t>Bharat Forge Limited</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>L93030DL2010PLC198141</t>
+          <t>L25209PN1961PLC012046</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>22-OCT-2024</t>
+          <t>08-AUG-2024</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>22-NOV-2024</t>
+          <t>08-NOV-2024</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>25-NOV-2024</t>
+          <t>04-DEC-2024</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>INE758T01015</t>
+          <t>INE465A01025</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -9082,12 +9078,12 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>BSE,NSE</t>
+          <t>NSE,BSE</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>ZOMATO</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -9102,60 +9098,60 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>85000000000</t>
+          <t>20000000000</t>
         </is>
       </c>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1318923_25112024021420_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1322769_04122024123600_WEB.xml</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>53948</t>
+          <t>54543</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>13-NOV-2024</t>
+          <t>03-DEC-2024</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>VARUN BEVERAGES LIMITED</t>
+          <t>Wonderla Holidays Limited</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>L74899DL1995PLC069839</t>
+          <t>L55101KA2002PLC031224</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>09-OCT-2024</t>
+          <t>04-OCT-2024</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>08-NOV-2024</t>
+          <t>09-NOV-2024</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>13-NOV-2024</t>
+          <t>03-DEC-2024</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>INE200M01039</t>
+          <t>INE066O01014</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -9170,12 +9166,12 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>WONDERLA</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>0.0005</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -9185,60 +9181,60 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>75000000000</t>
+          <t>6000000000</t>
         </is>
       </c>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1309045_13112024054044_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1322614_03122024065148_WEB.xml</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>53777</t>
+          <t>54480</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>07-NOV-2024</t>
+          <t>02-DEC-2024</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MCON RASAYAN INDIA LIMITED</t>
+          <t>Torrent Power Limited</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>L24304MH2016PLC286140</t>
+          <t>L31200GJ2004PLC044068</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>10-AUG-2024</t>
+          <t>22-MAY-2024</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>12-SEP-2024</t>
+          <t>30-JUL-2024</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>07-NOV-2024</t>
+          <t>02-DEC-2024</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>INE0O4M01019</t>
+          <t>INE813H01021</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -9248,12 +9244,12 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>NSE</t>
+          <t>BSE,NSE</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>MCON</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -9268,60 +9264,60 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>160000000</t>
+          <t>50000000000</t>
         </is>
       </c>
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1300260_07112024060124_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1321780_02122024124744_WEB.xml</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>53756</t>
+          <t>54261</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>06-NOV-2024</t>
+          <t>25-NOV-2024</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>WOCKHARDT LIMITED</t>
+          <t>KEI Industries Limited</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>L24230MH1999PLC120720</t>
+          <t>L74899DL1992PLC051527</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>28-MAY-2024</t>
+          <t>15-OCT-2024</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>28-JUN-2024</t>
+          <t>17-NOV-2024</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>06-NOV-2024</t>
+          <t>25-NOV-2024</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>INE049B01025</t>
+          <t>INE878B01027</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -9336,7 +9332,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>WOCKPHARMA</t>
+          <t>KEI</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -9351,60 +9347,60 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>10000000000</t>
+          <t>20000000000</t>
         </is>
       </c>
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1299253_06112024090745_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1319116_25112024050652_WEB.xml</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>53475</t>
+          <t>54258</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>24-OCT-2024</t>
+          <t>25-NOV-2024</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>360 ONE WAM LIMITED</t>
+          <t>ZOMATO LIMITED</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>L74140MH2008PLC177884</t>
+          <t>L93030DL2010PLC198141</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>19-SEP-2024</t>
+          <t>22-OCT-2024</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>20-OCT-2024</t>
+          <t>22-NOV-2024</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>24-OCT-2024</t>
+          <t>25-NOV-2024</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>INE466L01038</t>
+          <t>INE758T01015</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -9414,12 +9410,12 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>NSE,BSE</t>
+          <t>BSE,NSE</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>ZOMATO</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -9434,60 +9430,60 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>22500000000</t>
+          <t>85000000000</t>
         </is>
       </c>
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1287111_24102024043341_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1318923_25112024021420_WEB.xml</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>53477</t>
+          <t>53948</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>24-OCT-2024</t>
+          <t>13-NOV-2024</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Himatsingka Seide Limited</t>
+          <t>VARUN BEVERAGES LIMITED</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>L17112KA1985PLC006647</t>
+          <t>L74899DL1995PLC069839</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>25-JAN-2024</t>
+          <t>09-OCT-2024</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>01-MAR-2024</t>
+          <t>08-NOV-2024</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>24-OCT-2024</t>
+          <t>13-NOV-2024</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>INE049A01027</t>
+          <t>INE200M01039</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -9502,12 +9498,12 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>HIMATSEIDE</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0005</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -9517,60 +9513,60 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>4000000000</t>
+          <t>75000000000</t>
         </is>
       </c>
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1286937_24102024030725_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1309045_13112024054044_WEB.xml</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>53370</t>
+          <t>53777</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>21-OCT-2024</t>
+          <t>07-NOV-2024</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Epigral Limited</t>
+          <t>MCON RASAYAN INDIA LIMITED</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>L24100GJ2007PLC051717</t>
+          <t>L24304MH2016PLC286140</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>14-AUG-2024</t>
+          <t>10-AUG-2024</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>16-SEP-2024</t>
+          <t>12-SEP-2024</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>21-OCT-2024</t>
+          <t>07-NOV-2024</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>INE071N01016</t>
+          <t>INE0O4M01019</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -9580,12 +9576,12 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>BSE,NSE</t>
+          <t>NSE</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>EPIGRAL</t>
+          <t>MCON</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -9600,60 +9596,60 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>4000000000</t>
+          <t>160000000</t>
         </is>
       </c>
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1283614_21102024064529_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1300260_07112024060124_WEB.xml</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>53261</t>
+          <t>53756</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>18-OCT-2024</t>
+          <t>06-NOV-2024</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Pashupati Cotspin Limited</t>
+          <t>WOCKHARDT LIMITED</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>L17309GJ2017PLC098117</t>
+          <t>L24230MH1999PLC120720</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>03-AUG-2024</t>
+          <t>28-MAY-2024</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>07-SEP-2024</t>
+          <t>28-JUN-2024</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>17-OCT-2024</t>
+          <t>06-NOV-2024</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>INE124Y01010</t>
+          <t>INE049B01025</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -9663,12 +9659,12 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>NSE</t>
+          <t>BSE,NSE</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>PASHUPATI</t>
+          <t>WOCKPHARMA</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -9683,60 +9679,60 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>250000000</t>
+          <t>10000000000</t>
         </is>
       </c>
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1275957_17102024072032_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1299253_06112024090745_WEB.xml</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>53201</t>
+          <t>53475</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>15-OCT-2024</t>
+          <t>24-OCT-2024</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SKY GOLD LIMITED</t>
+          <t>360 ONE WAM LIMITED</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>L36911MH2008PLC181989</t>
+          <t>L74140MH2008PLC177884</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>09-AUG-2024</t>
+          <t>19-SEP-2024</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>02-SEP-2024</t>
+          <t>20-OCT-2024</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>15-OCT-2024</t>
+          <t>24-OCT-2024</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>INE01IU01018</t>
+          <t>INE466L01038</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -9746,12 +9742,12 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>BSE,NSE</t>
+          <t>NSE,BSE</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -9766,60 +9762,60 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>2700000000</t>
+          <t>22500000000</t>
         </is>
       </c>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1270961_15102024061724_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1287111_24102024043341_WEB.xml</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>53094</t>
+          <t>53477</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>10-OCT-2024</t>
+          <t>24-OCT-2024</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SANSERA ENGINEERING LIMITED</t>
+          <t>Himatsingka Seide Limited</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>L34103KA1981PLC004542</t>
+          <t>L17112KA1985PLC006647</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>20-AUG-2024</t>
+          <t>25-JAN-2024</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>26-SEP-2024</t>
+          <t>01-MAR-2024</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>10-OCT-2024</t>
+          <t>24-OCT-2024</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>INE953O01021</t>
+          <t>INE049A01027</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -9829,12 +9825,12 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>NSE,BSE</t>
+          <t>BSE,NSE</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>HIMATSEIDE</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -9849,60 +9845,60 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>12000000000</t>
+          <t>4000000000</t>
         </is>
       </c>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1265223_10102024061811_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1286937_24102024030725_WEB.xml</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>53034</t>
+          <t>53370</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>09-OCT-2024</t>
+          <t>21-OCT-2024</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Adani Enterprises Limited</t>
+          <t>Epigral Limited</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>L51100GJ1993PLC019067</t>
+          <t>L24100GJ2007PLC051717</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>28-MAY-2024</t>
+          <t>14-AUG-2024</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>24-JUN-2024</t>
+          <t>16-SEP-2024</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>09-OCT-2024</t>
+          <t>21-OCT-2024</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>INE423A01024</t>
+          <t>INE071N01016</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -9917,7 +9913,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>EPIGRAL</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -9932,18 +9928,184 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>166000000000</t>
+          <t>4000000000</t>
         </is>
       </c>
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1262960_09102024022518_WEB.xml</t>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1283614_21102024064529_WEB.xml</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>53261</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>18-OCT-2024</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Pashupati Cotspin Limited</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>L17309GJ2017PLC098117</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>03-AUG-2024</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>07-SEP-2024</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>17-OCT-2024</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>INE124Y01010</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>QIP</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>NSE</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>PASHUPATI</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>In-Principle</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>250000000</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1275957_17102024072032_WEB.xml</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>53201</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>15-OCT-2024</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>SKY GOLD LIMITED</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>L36911MH2008PLC181989</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>09-AUG-2024</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>02-SEP-2024</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>15-OCT-2024</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>INE01IU01018</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>QIP</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>BSE,NSE</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>SKYGOLD</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>In-Principle</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>2700000000</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/xbrl/QIP_IP_1270961_15102024061724_WEB.xml</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
